--- a/data/trans_bre/IP07_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-1,7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-0,97%</t>
+          <t>-2,2%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 9,12</t>
+          <t>-8,58; 8,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 3,77</t>
+          <t>-16,27; 3,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 7,18</t>
+          <t>-9,66; 7,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 10,56</t>
+          <t>-11,15; 8,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 11,61</t>
+          <t>-10,04; 11,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 4,73</t>
+          <t>-19,04; 5,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 8,95</t>
+          <t>-11,01; 9,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 14,45</t>
+          <t>-13,49; 11,18</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-7,31</t>
+          <t>-7,16</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-8,94%</t>
+          <t>-8,78%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 1,61</t>
+          <t>-17,27; 2,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 4,23</t>
+          <t>-14,5; 4,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 14,29</t>
+          <t>0,84; 14,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,19; 2,11</t>
+          <t>-17,4; 3,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,47; 2,04</t>
+          <t>-20,43; 2,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 5,24</t>
+          <t>-17,23; 5,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 17,33</t>
+          <t>1,09; 17,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 2,36</t>
+          <t>-20,32; 4,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>2,99</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 14,05</t>
+          <t>-7,59; 14,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 10,47</t>
+          <t>-9,79; 11,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 4,31</t>
+          <t>-12,06; 4,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 15,34</t>
+          <t>-9,38; 14,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 20,1</t>
+          <t>-9,73; 20,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 14,41</t>
+          <t>-11,89; 15,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 4,91</t>
+          <t>-12,9; 5,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 20,91</t>
+          <t>-10,75; 19,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,85</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>-0,43%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 7,66</t>
+          <t>-6,23; 7,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 8,39</t>
+          <t>-5,84; 8,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 2,98</t>
+          <t>-8,04; 2,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 10,89</t>
+          <t>-8,18; 7,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 10,25</t>
+          <t>-7,77; 10,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 12,5</t>
+          <t>-7,88; 12,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 3,67</t>
+          <t>-9,05; 3,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 15,02</t>
+          <t>-10,22; 9,79</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,78</t>
+          <t>10,32</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 14,38</t>
+          <t>-4,61; 14,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 15,44</t>
+          <t>-0,54; 16,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 10,57</t>
+          <t>-3,84; 10,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 25,25</t>
+          <t>-0,4; 22,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 21,81</t>
+          <t>-6,4; 21,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 22,89</t>
+          <t>-0,72; 24,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 13,74</t>
+          <t>-4,33; 13,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 44,33</t>
+          <t>-0,5; 38,5</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,57</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-3,38%</t>
+          <t>-1,59%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 14,64</t>
+          <t>-8,54; 13,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 6,37</t>
+          <t>-19,6; 6,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 14,18</t>
+          <t>-4,47; 15,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 9,86</t>
+          <t>-14,94; 11,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 21,64</t>
+          <t>-10,66; 20,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 8,82</t>
+          <t>-24,54; 7,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 18,28</t>
+          <t>-4,99; 19,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 14,3</t>
+          <t>-18,86; 16,48</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 4,89</t>
+          <t>-2,27; 5,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 3,56</t>
+          <t>-3,79; 3,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 3,65</t>
+          <t>-2,4; 3,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 6,67</t>
+          <t>-3,09; 5,56</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 6,56</t>
+          <t>-2,91; 7,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 4,83</t>
+          <t>-4,85; 4,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 4,33</t>
+          <t>-2,74; 4,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 9,13</t>
+          <t>-3,94; 7,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP07_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP07_R-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-6,54</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,17</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,29%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-7,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-1,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-2,2%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.2372618872613863</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-6.53654903812475</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.168528334093588</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.704520371545692</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.00288663443713291</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.0788765721475326</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.0137308604283992</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.02198073737456179</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,58; 8,78</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-16,27; 3,97</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-9,66; 7,71</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-11,15; 8,18</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-10,04; 11,31</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-19,04; 5,01</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-11,01; 9,32</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-13,49; 11,18</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.583134236511651</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-16.2719470672912</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-9.657220149337736</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-11.15152786390338</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.100408280213872</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1903721392422123</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.1100602044702067</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1349283229719707</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.778263967166234</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.969492899099234</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.71132013667295</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.184855362727719</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1131319705618059</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.05007472643814295</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.09324358051940655</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.1118362854551925</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-7,62</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-5,64</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,68</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-7,16</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-9,24%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-6,92%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-8,78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-17,27; 2,35</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-14,5; 4,18</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,84; 14,13</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-17,4; 3,28</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-20,43; 2,86</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-17,23; 5,19</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,09; 17,41</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-20,32; 4,18</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-7.622668988648307</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-5.635511721925113</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7.682524687949543</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-7.164430191426341</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.09235409058709058</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.06917917350357158</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.08909563182441377</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.08781672291139644</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,11</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,28</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,99</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-3,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-17.26993928241266</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-14.50466649784183</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8449447574272388</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-17.39580620469168</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2042552578401175</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1722857220747715</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.01090340038579822</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2032116783504004</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,59; 14,27</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-9,79; 11,53</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-12,06; 4,52</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-9,38; 14,11</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-9,73; 20,18</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-11,89; 15,92</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-12,9; 5,1</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-10,75; 19,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.349426732292249</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.181472261864835</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>14.12869848690815</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.275256438719099</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.02855435616868512</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.05186701927224183</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.1740995402501544</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.0418189721727209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,84</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-3,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-0,43%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>4.113814328220622</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4995753971468897</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.277261714988355</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2.986845185313414</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.05466309350435795</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.006489074119198955</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.03554325544134737</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.03636711340980483</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,23; 7,47</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,84; 8,13</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-8,04; 2,7</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,18; 7,02</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-7,77; 10,08</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-7,88; 12,06</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-9,05; 3,26</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-10,22; 9,79</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.585253802600151</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-9.791045492891612</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-12.06254509683273</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.383170461605729</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.09732338310665323</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1189100700199673</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.1289565091168408</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1075257325296572</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>14.26672395025098</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.52811647340816</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.517163182448388</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>14.10595223731251</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.2017941139053942</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.159178669445847</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.05101404971688508</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.1901920950072472</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5,31</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7,87</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,86</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,32</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-4,61; 14,36</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,54; 16,37</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,84; 10,11</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 22,24</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-6,4; 21,07</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,72; 24,67</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-4,33; 13,23</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-0,5; 38,5</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>1.04646142491237</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9804491551416827</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.837654380400878</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.3282789362654803</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.01352325440526453</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.01381453183629822</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.03283510089320811</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.004286037083243323</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2,9</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-7,07</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5,3</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-9,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-1,59%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.231198398939915</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.841907136245304</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-8.036299744569355</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.18272530609892</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.07767164714111374</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.07880509762176971</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.09053750692226427</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1022354010362161</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-8,54; 13,69</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-19,6; 6,01</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-4,47; 15,25</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-14,94; 11,35</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-10,66; 20,69</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-24,54; 7,67</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-4,99; 19,58</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-18,86; 16,48</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.465251865565699</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.129050552321942</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.702935359709639</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.023181429441657</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1008390026624722</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1205810409918899</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.03257554949027033</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.09785602114460229</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1019,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>5.308260133953635</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7.873659614384454</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.858817474490305</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>10.32239914626</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.07463025591963819</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1096362193865467</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.03467446100983568</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.1507625410328438</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,27; 5,25</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,79; 3,61</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 3,81</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-3,09; 5,56</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-2,91; 7,1</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-4,85; 4,86</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-2,74; 4,49</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-3,94; 7,62</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-4.606319904285648</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.5366423450232679</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.841370986023001</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.4020442961390824</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.06396673422301132</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.007197603172754257</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.04332172619082666</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.005043544168389048</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>14.36401506243969</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>16.36932046332975</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>10.11389179044438</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>22.24096169694485</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.2106822742826652</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2467342492901988</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.132270968667305</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3850054021996328</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2.900230040630858</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-7.070273170382357</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>5.300312687132102</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.177003092778472</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.03932388597948482</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.09048109668438289</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.06277879945274507</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.01591795024184401</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-8.537262924691774</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-19.60192974915912</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-4.473973993629283</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-14.94105567780759</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.1066302487765831</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.2453899389808832</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.04988671226862234</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.1885642411100588</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>13.68642887763336</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>6.009567939138657</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>15.25126573067301</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>11.35246061933683</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.2068655981326952</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.07668859051407069</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.1957691208806849</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.164848331910726</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1.231927697653845</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.1194726881753372</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.8125894526958555</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.8841953889781373</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.01602845636081438</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.001582005563861393</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.009467435093871917</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.01165383521310236</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.266840507050085</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.791762848380516</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-2.400787801808008</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-3.089404093589418</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.02913622401613395</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.04852864858645793</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.02736916234005507</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.03935554340918223</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>5.25465844356134</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.60962372094285</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>3.811097683028344</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>5.557218838511217</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.07101323832961157</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.04858730894085043</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.04492955922957207</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.07622184514516947</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
